--- a/Assets/Resources/DataFiles/CharData/ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ExcelFile/EnemyData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\ExcelFile\Class\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D92E29C-A8A2-4A54-9392-4A77A5277C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3DA185-3B37-4D16-B7EB-4159FDBEDBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{669DFCCE-93B3-497D-B1CD-A661736B07BB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{669DFCCE-93B3-497D-B1CD-A661736B07BB}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,10 +170,6 @@
   </si>
   <si>
     <t>attackRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attackCDR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -604,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC567DD-038D-4BE5-B4F7-861058B1AE7F}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.69921875" style="1" customWidth="1"/>
@@ -618,12 +614,11 @@
     <col min="9" max="9" width="15.59765625" style="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.59765625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.3984375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="12" max="12" width="18" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,13 +653,10 @@
         <v>3</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -701,11 +693,8 @@
       <c r="L2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1001</v>
       </c>
@@ -742,11 +731,8 @@
       <c r="L3" s="1">
         <v>1</v>
       </c>
-      <c r="M3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>1002</v>
       </c>
@@ -781,13 +767,10 @@
         <v>1.5</v>
       </c>
       <c r="L4" s="1">
-        <v>1</v>
-      </c>
-      <c r="M4" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>1003</v>
       </c>
@@ -822,13 +805,10 @@
         <v>4</v>
       </c>
       <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>1004</v>
       </c>
@@ -863,9 +843,6 @@
         <v>7</v>
       </c>
       <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
         <v>4</v>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/CharData/ExcelFile/EnemyData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ExcelFile/EnemyData.xlsx
@@ -1,179 +1,169 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Desktop\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub\Project2\Assets\Resources\DataFiles\CharData\ExcelFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3DA185-3B37-4D16-B7EB-4159FDBEDBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6F372A-1653-4458-B738-0F158DB66E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{669DFCCE-93B3-497D-B1CD-A661736B07BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnemyData" sheetId="1" r:id="rId1"/>
-    <sheet name="ComboBox" sheetId="4" r:id="rId2"/>
+    <sheet name="ComboBox" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemyName</t>
+  </si>
+  <si>
+    <t>enemyGrade</t>
+  </si>
+  <si>
+    <t>attackType</t>
+  </si>
+  <si>
+    <t>baseHp</t>
+  </si>
+  <si>
+    <t>baseATK</t>
+  </si>
+  <si>
+    <t>baseDEF</t>
+  </si>
+  <si>
+    <t>baseMS</t>
+  </si>
+  <si>
+    <t>baseAS</t>
+  </si>
+  <si>
+    <t>attackRange</t>
+  </si>
+  <si>
+    <t>attackCDR</t>
+  </si>
+  <si>
+    <t>patternId</t>
+  </si>
+  <si>
+    <t>정찰 드론</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>작업 기계</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t>포크 레인</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>Badass Mecha MK 1</t>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>baseHp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemyId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemyName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemyName_kr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemyGrade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attackType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Melee</t>
-  </si>
-  <si>
-    <t>Ranged</t>
-  </si>
-  <si>
-    <t>baseATK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>baseDEF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>baseMS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>baseAS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정찰 드론</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Patrol Drone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>EnemyGrade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackType</t>
   </si>
   <si>
     <t>Common</t>
   </si>
   <si>
-    <t>Common</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Advanced</t>
-  </si>
-  <si>
-    <t>Advanced</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Elite</t>
-  </si>
-  <si>
-    <t>Elite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>AttackType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Working Machine</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업 기계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Excavator</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포크 레인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Badass Mecha MK 1</t>
-  </si>
-  <si>
-    <t>Badass Mecha MK 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hidden</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attackRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>patternId</t>
+  </si>
+  <si>
+    <t>enemy.normal.ranged.patrol_drone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.advanced.melee.working_machine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.elite.melee.excavator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.boss.badass_mecha_mk1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.normal.melee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.normal.ranged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.advanced.melee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.advanced.ranged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.elite.melee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.elite.ranged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.boss.melee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.boss.ranged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.hidden.melee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy.hidden.ranged</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemyID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -181,7 +171,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,13 +186,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -250,7 +233,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -260,12 +243,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -599,22 +584,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC567DD-038D-4BE5-B4F7-861058B1AE7F}">
-  <dimension ref="A1:L6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="41.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.09765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.3984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.69921875" customWidth="1"/>
-    <col min="6" max="6" width="11.8984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.09765625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.69921875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.8984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.09765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.59765625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.59765625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.796875" style="1" customWidth="1"/>
     <col min="13" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
@@ -623,311 +608,337 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1">
+        <v>300</v>
+      </c>
+      <c r="F3" s="1">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1">
-        <v>300</v>
-      </c>
-      <c r="G3" s="1">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1">
-        <v>30</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A4" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
+      <c r="E4" s="1">
+        <v>500</v>
       </c>
       <c r="F4" s="1">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H4" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J4" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="K4" s="1">
         <v>1.5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
       <c r="L4" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A5" s="1">
-        <v>1003</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>29</v>
+      <c r="A5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
+      </c>
+      <c r="E5" s="1">
+        <v>800</v>
       </c>
       <c r="F5" s="1">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="G5" s="1">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H5" s="1">
-        <v>120</v>
+        <v>0.5</v>
       </c>
       <c r="I5" s="1">
         <v>0.5</v>
       </c>
       <c r="J5" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="K5" s="1">
         <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A6" s="1">
-        <v>1004</v>
+      <c r="A6" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1500</v>
       </c>
       <c r="F6" s="1">
-        <v>1500</v>
+        <v>75</v>
       </c>
       <c r="G6" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>1.5</v>
       </c>
       <c r="I6" s="1">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J6" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="K6" s="1">
         <v>7</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
       </c>
       <c r="L6" s="1">
         <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A13" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A14" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A15" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5315A52E-F50A-46B9-9036-4049EFF8A3AE}">
-          <x14:formula1>
-            <xm:f>ComboBox!$A$2:$A$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>D7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{95866C19-93A0-468E-9033-7C6ED713F907}">
-          <x14:formula1>
-            <xm:f>ComboBox!$B$2:$B$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E6</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A205DBDE-2A0E-4CA3-B4B4-698087922AE9}">
-          <x14:formula1>
-            <xm:f>ComboBox!$A$2:$A$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>D3:D6</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC40901-E8EB-4ABE-AF79-9505FA576532}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1"/>
     </row>
